--- a/Lab/Test Scores.xlsx
+++ b/Lab/Test Scores.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="6800"/>
+    <workbookView windowWidth="18350" windowHeight="6880"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -1285,9 +1285,9 @@
       <c r="A13" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="8" t="str" cm="1">
-        <f t="array" ref="B13">_xlfn.IFS(B5&gt;77%,"Good",B5&lt;70%,"Bad")</f>
-        <v>Good</v>
+      <c r="B13" s="8" t="e" cm="1">
+        <f t="array" ref="B13">_xlfn.IFS(B35&gt;77%,"Good",B5&lt;70%,"Bad")</f>
+        <v>#N/A</v>
       </c>
       <c r="C13" s="8" t="str" cm="1">
         <f t="array" ref="C13">_xlfn.IFS(B5&gt;77%,"Good",B5&lt;70%,"Bad")</f>
